--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE468AD7-C674-4281-AB03-D5199C511061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D633E42-4043-4A17-A810-37EEA41930CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13724" uniqueCount="5965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14427" uniqueCount="6265">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
   <si>
-    <t>Period: 01/01/26 00:00 CST - 12/31/26 23:59 CST</t>
+    <t>Period: 01/01/26 02:00 CST - 01/01/27 23:59 CST</t>
   </si>
   <si>
     <t>Datetime</t>
@@ -17915,6 +17915,906 @@
   </si>
   <si>
     <t>08/24/26 06:17 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 09:23 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1787581382126</t>
+  </si>
+  <si>
+    <t>39.368825, -94.581902</t>
+  </si>
+  <si>
+    <t>08/24/26 18:12 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 10:30 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787585426113</t>
+  </si>
+  <si>
+    <t>1mi W of Liberty MO</t>
+  </si>
+  <si>
+    <t>39.239237, -94.437782</t>
+  </si>
+  <si>
+    <t>08/24/26 18:29 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 10:57 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1787587026733</t>
+  </si>
+  <si>
+    <t>3.3mi E of Gladstone MO</t>
+  </si>
+  <si>
+    <t>39.225253, -94.500370</t>
+  </si>
+  <si>
+    <t>08/24/26 18:13 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 14:52 CDT</t>
+  </si>
+  <si>
+    <t>281475000719319-1787601148424</t>
+  </si>
+  <si>
+    <t>39.242364, -94.524942</t>
+  </si>
+  <si>
+    <t>08/24/26 18:26 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 16:18 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787606315284</t>
+  </si>
+  <si>
+    <t>39.289828, -94.681246</t>
+  </si>
+  <si>
+    <t>08/24/26 16:38 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787607517015</t>
+  </si>
+  <si>
+    <t>39.367277, -94.784008</t>
+  </si>
+  <si>
+    <t>08/24/26 18:23 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 17:24 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787610283474</t>
+  </si>
+  <si>
+    <t>3.6mi S of Independence MO</t>
+  </si>
+  <si>
+    <t>39.036505, -94.362064</t>
+  </si>
+  <si>
+    <t>08/24/26 18:20 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 17:35 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1787610928527</t>
+  </si>
+  <si>
+    <t>4.5mi NW of Parkville MO</t>
+  </si>
+  <si>
+    <t>39.248816, -94.779014</t>
+  </si>
+  <si>
+    <t>08/24/26 18:21 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 17:44 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787611478177</t>
+  </si>
+  <si>
+    <t>38.946127, -94.359407</t>
+  </si>
+  <si>
+    <t>08/24/26 18:28 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 18:35 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787614543327</t>
+  </si>
+  <si>
+    <t>3.2mi SW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>39.185593, -94.606100</t>
+  </si>
+  <si>
+    <t>08/25/26 06:06 CDT</t>
+  </si>
+  <si>
+    <t>08/24/26 19:09 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787616590392</t>
+  </si>
+  <si>
+    <t>39.368168, -94.772381</t>
+  </si>
+  <si>
+    <t>08/25/26 02:53 CDT</t>
+  </si>
+  <si>
+    <t>281474984523377-1787644387054</t>
+  </si>
+  <si>
+    <t>39.246619, -94.630773</t>
+  </si>
+  <si>
+    <t>08/25/26 08:50 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787665805685</t>
+  </si>
+  <si>
+    <t>39.246592, -94.537678</t>
+  </si>
+  <si>
+    <t>08/25/26 22:39 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 09:42 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787668947180</t>
+  </si>
+  <si>
+    <t>39.181511, -94.613374</t>
+  </si>
+  <si>
+    <t>08/25/26 22:36 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 09:48 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787669311845</t>
+  </si>
+  <si>
+    <t>39.210441, -94.641354</t>
+  </si>
+  <si>
+    <t>08/25/26 22:35 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 12:17 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787678268896</t>
+  </si>
+  <si>
+    <t>4.8mi N of Smithville MO</t>
+  </si>
+  <si>
+    <t>39.461442, -94.567506</t>
+  </si>
+  <si>
+    <t>08/25/26 12:42 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787679722225</t>
+  </si>
+  <si>
+    <t>3.5mi NW of Kansas City MO</t>
+  </si>
+  <si>
+    <t>39.165471, -94.592307</t>
+  </si>
+  <si>
+    <t>08/25/26 22:43 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 15:18 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787689105561</t>
+  </si>
+  <si>
+    <t>3.5mi E of Kansas City KS</t>
+  </si>
+  <si>
+    <t>39.122386, -94.678129</t>
+  </si>
+  <si>
+    <t>08/25/26 22:37 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 22:44 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 16:41 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787694076887</t>
+  </si>
+  <si>
+    <t>1.1mi SW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>39.204511, -94.576402</t>
+  </si>
+  <si>
+    <t>08/25/26 19:00 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787702458439</t>
+  </si>
+  <si>
+    <t>39.352069, -94.695423</t>
+  </si>
+  <si>
+    <t>08/25/26 19:56 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787705811049</t>
+  </si>
+  <si>
+    <t>2.7mi SW of Smithville MO</t>
+  </si>
+  <si>
+    <t>39.368931, -94.615091</t>
+  </si>
+  <si>
+    <t>08/25/26 20:03 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787706202859</t>
+  </si>
+  <si>
+    <t>7.9mi W of Smithville MO</t>
+  </si>
+  <si>
+    <t>39.354301, -94.714553</t>
+  </si>
+  <si>
+    <t>08/26/26 10:18 CDT</t>
+  </si>
+  <si>
+    <t>281474980798123-1787757491943</t>
+  </si>
+  <si>
+    <t>1.9mi S of Gardner KS</t>
+  </si>
+  <si>
+    <t>38.784349, -94.923611</t>
+  </si>
+  <si>
+    <t>08/26/26 10:32 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787758331631</t>
+  </si>
+  <si>
+    <t>39.151279, -94.536476</t>
+  </si>
+  <si>
+    <t>08/26/26 18:55 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 12:03 CDT</t>
+  </si>
+  <si>
+    <t>281474992542337-1787763819615</t>
+  </si>
+  <si>
+    <t>4.9mi E of Kansas City KS</t>
+  </si>
+  <si>
+    <t>39.147321, -94.658712</t>
+  </si>
+  <si>
+    <t>08/26/26 18:56 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 12:21 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787764906742</t>
+  </si>
+  <si>
+    <t>39.294201, -94.684203</t>
+  </si>
+  <si>
+    <t>08/26/26 18:57 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 13:51 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787770282965</t>
+  </si>
+  <si>
+    <t>2.3mi SE of St. Joseph MO</t>
+  </si>
+  <si>
+    <t>39.729933, -94.800975</t>
+  </si>
+  <si>
+    <t>08/26/26 18:58 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 14:59 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787774379647</t>
+  </si>
+  <si>
+    <t>0.2mi SE of Gladstone MO</t>
+  </si>
+  <si>
+    <t>39.211229, -94.557666</t>
+  </si>
+  <si>
+    <t>08/26/26 19:07 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 15:20 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787775657943</t>
+  </si>
+  <si>
+    <t>39.257952, -94.651005</t>
+  </si>
+  <si>
+    <t>08/26/26 19:10 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 15:52 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787777558413</t>
+  </si>
+  <si>
+    <t>39.356573, -94.766955</t>
+  </si>
+  <si>
+    <t>08/26/26 19:03 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 16:46 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787780818892</t>
+  </si>
+  <si>
+    <t>39.281207, -94.674949</t>
+  </si>
+  <si>
+    <t>08/26/26 16:48 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787780882326</t>
+  </si>
+  <si>
+    <t>39.294240, -94.684224</t>
+  </si>
+  <si>
+    <t>08/26/26 18:59 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 16:49 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787780945573</t>
+  </si>
+  <si>
+    <t>39.294939, -94.685356</t>
+  </si>
+  <si>
+    <t>08/26/26 19:11 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 17:08 CDT</t>
+  </si>
+  <si>
+    <t>281474986458584-1787782088664</t>
+  </si>
+  <si>
+    <t>3.9mi E of Bonner Springs KS</t>
+  </si>
+  <si>
+    <t>39.093363, -94.807376</t>
+  </si>
+  <si>
+    <t>08/26/26 19:04 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 17:36 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787783819229</t>
+  </si>
+  <si>
+    <t>39.246994, -94.652797</t>
+  </si>
+  <si>
+    <t>08/26/26 19:12 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 17:43 CDT</t>
+  </si>
+  <si>
+    <t>281475000719319-1787784210618</t>
+  </si>
+  <si>
+    <t>39.181253, -94.575973</t>
+  </si>
+  <si>
+    <t>08/26/26 19:00 CDT</t>
+  </si>
+  <si>
+    <t>08/26/26 21:55 CDT</t>
+  </si>
+  <si>
+    <t>9001-MDrollback</t>
+  </si>
+  <si>
+    <t>281475006025017-1787799355395</t>
+  </si>
+  <si>
+    <t>39.450080, -94.788656</t>
+  </si>
+  <si>
+    <t>08/27/26 07:17 CDT</t>
+  </si>
+  <si>
+    <t>08/27/26 08:48 CDT</t>
+  </si>
+  <si>
+    <t>281475006025017-1787838480376</t>
+  </si>
+  <si>
+    <t>8.1mi S of St. Joseph MO</t>
+  </si>
+  <si>
+    <t>39.644906, -94.787727</t>
+  </si>
+  <si>
+    <t>08/27/26 20:44 CDT</t>
+  </si>
+  <si>
+    <t>08/27/26 09:07 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787839679040</t>
+  </si>
+  <si>
+    <t>39.246459, -94.537269</t>
+  </si>
+  <si>
+    <t>08/27/26 10:27 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787844421100</t>
+  </si>
+  <si>
+    <t>39.253963, -94.649510</t>
+  </si>
+  <si>
+    <t>08/27/26 10:52 CDT</t>
+  </si>
+  <si>
+    <t>281474987560362-1787845939745</t>
+  </si>
+  <si>
+    <t>4.2mi SE of Kansas City MO</t>
+  </si>
+  <si>
+    <t>39.091946, -94.487803</t>
+  </si>
+  <si>
+    <t>08/27/26 20:45 CDT</t>
+  </si>
+  <si>
+    <t>08/27/26 13:56 CDT</t>
+  </si>
+  <si>
+    <t>281474983617430-1787856981105</t>
+  </si>
+  <si>
+    <t>1mi E of Shawnee KS</t>
+  </si>
+  <si>
+    <t>39.011572, -94.788831</t>
+  </si>
+  <si>
+    <t>08/27/26 20:48 CDT</t>
+  </si>
+  <si>
+    <t>08/27/26 18:19 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787872776347</t>
+  </si>
+  <si>
+    <t>39.272679, -94.467020</t>
+  </si>
+  <si>
+    <t>08/27/26 20:52 CDT</t>
+  </si>
+  <si>
+    <t>08/27/26 19:06 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787875563995</t>
+  </si>
+  <si>
+    <t>0.1mi S of Merriam KS</t>
+  </si>
+  <si>
+    <t>39.016771, -94.693325</t>
+  </si>
+  <si>
+    <t>08/27/26 19:08 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787875728227</t>
+  </si>
+  <si>
+    <t>1.1mi W of Merriam KS</t>
+  </si>
+  <si>
+    <t>39.014823, -94.712567</t>
+  </si>
+  <si>
+    <t>08/27/26 19:47 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787878057694</t>
+  </si>
+  <si>
+    <t>39.259452, -94.575706</t>
+  </si>
+  <si>
+    <t>08/28/26 01:18 CDT</t>
+  </si>
+  <si>
+    <t>281475006025017-1787897905314</t>
+  </si>
+  <si>
+    <t>3.6mi NE of Leavenworth KS</t>
+  </si>
+  <si>
+    <t>39.349208, -94.865339</t>
+  </si>
+  <si>
+    <t>08/28/26 08:14 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 02:07 CDT</t>
+  </si>
+  <si>
+    <t>281475006025017-1787900872450</t>
+  </si>
+  <si>
+    <t>39.394940, -94.789450</t>
+  </si>
+  <si>
+    <t>08/28/26 07:16 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787919401970</t>
+  </si>
+  <si>
+    <t>2.7mi N of Parkville MO</t>
+  </si>
+  <si>
+    <t>39.238575, -94.733327</t>
+  </si>
+  <si>
+    <t>08/28/26 08:16 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 08:22 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1787923320278</t>
+  </si>
+  <si>
+    <t>39.291906, -94.585119</t>
+  </si>
+  <si>
+    <t>08/28/26 23:19 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1787923369676</t>
+  </si>
+  <si>
+    <t>6.2mi N of Gladstone MO</t>
+  </si>
+  <si>
+    <t>39.301798, -94.582963</t>
+  </si>
+  <si>
+    <t>08/28/26 09:09 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787926171147</t>
+  </si>
+  <si>
+    <t>39.196746, -94.505906</t>
+  </si>
+  <si>
+    <t>08/28/26 23:20 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 09:33 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787927624951</t>
+  </si>
+  <si>
+    <t>38.977268, -94.713214</t>
+  </si>
+  <si>
+    <t>08/28/26 23:22 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 11:15 CDT</t>
+  </si>
+  <si>
+    <t>281475006025017-1787933734568</t>
+  </si>
+  <si>
+    <t>1.3mi S of Olathe KS</t>
+  </si>
+  <si>
+    <t>38.865893, -94.812000</t>
+  </si>
+  <si>
+    <t>08/28/26 11:40 CDT</t>
+  </si>
+  <si>
+    <t>281475000719319-1787935242999</t>
+  </si>
+  <si>
+    <t>4.9mi SW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>39.174696, -94.635384</t>
+  </si>
+  <si>
+    <t>08/28/26 12:26 CDT</t>
+  </si>
+  <si>
+    <t>281474992542337-1787937998727</t>
+  </si>
+  <si>
+    <t>24.5mi SW of Maryville MO</t>
+  </si>
+  <si>
+    <t>40.156176, -95.265158</t>
+  </si>
+  <si>
+    <t>08/28/26 13:05 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787940321638</t>
+  </si>
+  <si>
+    <t>39.251660, -94.631034</t>
+  </si>
+  <si>
+    <t>08/28/26 23:24 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 13:09 CDT</t>
+  </si>
+  <si>
+    <t>281474980616004-1787940546979</t>
+  </si>
+  <si>
+    <t>1.5mi S of Olathe KS</t>
+  </si>
+  <si>
+    <t>38.862743, -94.812111</t>
+  </si>
+  <si>
+    <t>08/28/26 13:32 CDT</t>
+  </si>
+  <si>
+    <t>281474980531321-1787941978625</t>
+  </si>
+  <si>
+    <t>39.257923, -94.598235</t>
+  </si>
+  <si>
+    <t>08/28/26 14:26 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787945161426</t>
+  </si>
+  <si>
+    <t>39.232319, -94.464909</t>
+  </si>
+  <si>
+    <t>08/28/26 23:25 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 14:47 CDT</t>
+  </si>
+  <si>
+    <t>281475006025017-1787946434767</t>
+  </si>
+  <si>
+    <t>3.6mi SE of Lenexa KS</t>
+  </si>
+  <si>
+    <t>38.916932, -94.766561</t>
+  </si>
+  <si>
+    <t>08/28/26 14:57 CDT</t>
+  </si>
+  <si>
+    <t>281474980616004-1787947055282</t>
+  </si>
+  <si>
+    <t>3mi N of Spring Hill KS</t>
+  </si>
+  <si>
+    <t>38.799998, -94.824816</t>
+  </si>
+  <si>
+    <t>08/28/26 23:26 CDT</t>
+  </si>
+  <si>
+    <t>08/29/26 06:50 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 15:01 CDT</t>
+  </si>
+  <si>
+    <t>281474982794920-1787947297633</t>
+  </si>
+  <si>
+    <t>39.370725, -94.788029</t>
+  </si>
+  <si>
+    <t>08/28/26 23:28 CDT</t>
+  </si>
+  <si>
+    <t>08/29/26 09:29 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 15:25 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787948727006</t>
+  </si>
+  <si>
+    <t>39.248317, -94.545269</t>
+  </si>
+  <si>
+    <t>08/28/26 23:30 CDT</t>
+  </si>
+  <si>
+    <t>281474980531320-1787948738872</t>
+  </si>
+  <si>
+    <t>39.250583, -94.549460</t>
+  </si>
+  <si>
+    <t>08/28/26 16:21 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787952084387</t>
+  </si>
+  <si>
+    <t>39.197055, -94.492495</t>
+  </si>
+  <si>
+    <t>08/28/26 18:12 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1787958728894</t>
+  </si>
+  <si>
+    <t>39.178152, -94.565085</t>
+  </si>
+  <si>
+    <t>08/28/26 19:45 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1787964326780</t>
+  </si>
+  <si>
+    <t>39.259850, -94.583072</t>
+  </si>
+  <si>
+    <t>08/29/26 09:55 CDT</t>
+  </si>
+  <si>
+    <t>281475000719319-1788015349019</t>
+  </si>
+  <si>
+    <t>2.6mi NW of Olathe KS</t>
+  </si>
+  <si>
+    <t>38.912684, -94.850225</t>
+  </si>
+  <si>
+    <t>08/29/26 13:51 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1788029480003</t>
+  </si>
+  <si>
+    <t>39.273238, -94.575696</t>
+  </si>
+  <si>
+    <t>08/29/26 18:08 CDT</t>
+  </si>
+  <si>
+    <t>281474980531324-1788044913644</t>
+  </si>
+  <si>
+    <t>39.259819, -94.583063</t>
+  </si>
+  <si>
+    <t>08/30/26 10:03 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1788102218055</t>
+  </si>
+  <si>
+    <t>39.254083, -94.624476</t>
+  </si>
+  <si>
+    <t>08/30/26 12:25 CDT</t>
+  </si>
+  <si>
+    <t>281474980531318-1788110717559</t>
+  </si>
+  <si>
+    <t>39.178701, -94.528677</t>
+  </si>
+  <si>
+    <t>08/30/26 18:02 CDT</t>
+  </si>
+  <si>
+    <t>281474992542337-1788130943732</t>
+  </si>
+  <si>
+    <t>39.302439, -94.582441</t>
+  </si>
+  <si>
+    <t>08/31/26 07:42 CDT</t>
+  </si>
+  <si>
+    <t>281475006025017-1788180173625</t>
+  </si>
+  <si>
+    <t>6.8mi S of St. Joseph MO</t>
+  </si>
+  <si>
+    <t>39.665207, -94.787919</t>
   </si>
 </sst>
 </file>
@@ -18276,7 +19176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1449"/>
+  <dimension ref="A1:N1524"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -75246,6 +76146,2952 @@
       </c>
       <c r="N1449" s="3"/>
     </row>
+    <row r="1450" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1450" s="3" t="s">
+        <v>5965</v>
+      </c>
+      <c r="B1450" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1450" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1450" s="3" t="s">
+        <v>5966</v>
+      </c>
+      <c r="E1450" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1450" s="3" t="s">
+        <v>4752</v>
+      </c>
+      <c r="G1450" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="H1450" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1450" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1450" s="3"/>
+      <c r="K1450" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1450" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1450" s="3" t="s">
+        <v>5968</v>
+      </c>
+      <c r="N1450" s="3"/>
+    </row>
+    <row r="1451" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1451" s="3" t="s">
+        <v>5969</v>
+      </c>
+      <c r="B1451" s="3"/>
+      <c r="C1451" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1451" s="3" t="s">
+        <v>5970</v>
+      </c>
+      <c r="E1451" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1451" s="3" t="s">
+        <v>5971</v>
+      </c>
+      <c r="G1451" s="3" t="s">
+        <v>5972</v>
+      </c>
+      <c r="H1451" s="3"/>
+      <c r="I1451" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1451" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1451" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1451" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1451" s="3" t="s">
+        <v>5973</v>
+      </c>
+      <c r="N1451" s="3"/>
+    </row>
+    <row r="1452" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1452" s="3" t="s">
+        <v>5974</v>
+      </c>
+      <c r="B1452" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1452" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1452" s="3" t="s">
+        <v>5975</v>
+      </c>
+      <c r="E1452" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1452" s="3" t="s">
+        <v>5976</v>
+      </c>
+      <c r="G1452" s="3" t="s">
+        <v>5977</v>
+      </c>
+      <c r="H1452" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1452" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1452" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1452" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1452" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1452" s="3" t="s">
+        <v>5978</v>
+      </c>
+      <c r="N1452" s="3"/>
+    </row>
+    <row r="1453" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1453" s="3" t="s">
+        <v>5979</v>
+      </c>
+      <c r="B1453" s="3"/>
+      <c r="C1453" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1453" s="3" t="s">
+        <v>5980</v>
+      </c>
+      <c r="E1453" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1453" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="G1453" s="3" t="s">
+        <v>5981</v>
+      </c>
+      <c r="H1453" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1453" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1453" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1453" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1453" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1453" s="3" t="s">
+        <v>5982</v>
+      </c>
+      <c r="N1453" s="3"/>
+    </row>
+    <row r="1454" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1454" s="3" t="s">
+        <v>5983</v>
+      </c>
+      <c r="B1454" s="3"/>
+      <c r="C1454" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1454" s="3" t="s">
+        <v>5984</v>
+      </c>
+      <c r="E1454" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1454" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G1454" s="3" t="s">
+        <v>5985</v>
+      </c>
+      <c r="H1454" s="3"/>
+      <c r="I1454" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1454" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1454" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1454" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1454" s="3" t="s">
+        <v>5973</v>
+      </c>
+      <c r="N1454" s="3"/>
+    </row>
+    <row r="1455" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1455" s="3" t="s">
+        <v>5986</v>
+      </c>
+      <c r="B1455" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C1455" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1455" s="3" t="s">
+        <v>5987</v>
+      </c>
+      <c r="E1455" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1455" s="3" t="s">
+        <v>3018</v>
+      </c>
+      <c r="G1455" s="3" t="s">
+        <v>5988</v>
+      </c>
+      <c r="H1455" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1455" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1455" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1455" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1455" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1455" s="3" t="s">
+        <v>5989</v>
+      </c>
+      <c r="N1455" s="3"/>
+    </row>
+    <row r="1456" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1456" s="3" t="s">
+        <v>5990</v>
+      </c>
+      <c r="B1456" s="3"/>
+      <c r="C1456" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1456" s="3" t="s">
+        <v>5991</v>
+      </c>
+      <c r="E1456" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1456" s="3" t="s">
+        <v>5992</v>
+      </c>
+      <c r="G1456" s="3" t="s">
+        <v>5993</v>
+      </c>
+      <c r="H1456" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1456" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1456" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1456" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1456" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1456" s="3" t="s">
+        <v>5994</v>
+      </c>
+      <c r="N1456" s="3"/>
+    </row>
+    <row r="1457" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1457" s="3" t="s">
+        <v>5995</v>
+      </c>
+      <c r="B1457" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1457" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1457" s="3" t="s">
+        <v>5996</v>
+      </c>
+      <c r="E1457" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1457" s="3" t="s">
+        <v>5997</v>
+      </c>
+      <c r="G1457" s="3" t="s">
+        <v>5998</v>
+      </c>
+      <c r="H1457" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1457" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1457" s="3"/>
+      <c r="K1457" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1457" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1457" s="3" t="s">
+        <v>5999</v>
+      </c>
+      <c r="N1457" s="3"/>
+    </row>
+    <row r="1458" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1458" s="3" t="s">
+        <v>6000</v>
+      </c>
+      <c r="B1458" s="3"/>
+      <c r="C1458" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1458" s="3" t="s">
+        <v>6001</v>
+      </c>
+      <c r="E1458" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1458" s="3" t="s">
+        <v>5218</v>
+      </c>
+      <c r="G1458" s="3" t="s">
+        <v>6002</v>
+      </c>
+      <c r="H1458" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1458" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1458" s="3"/>
+      <c r="K1458" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1458" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1458" s="3" t="s">
+        <v>6003</v>
+      </c>
+      <c r="N1458" s="3"/>
+    </row>
+    <row r="1459" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1459" s="3" t="s">
+        <v>6004</v>
+      </c>
+      <c r="B1459" s="3"/>
+      <c r="C1459" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1459" s="3" t="s">
+        <v>6005</v>
+      </c>
+      <c r="E1459" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1459" s="3" t="s">
+        <v>6006</v>
+      </c>
+      <c r="G1459" s="3" t="s">
+        <v>6007</v>
+      </c>
+      <c r="H1459" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1459" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1459" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1459" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1459" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1459" s="3" t="s">
+        <v>6008</v>
+      </c>
+      <c r="N1459" s="3"/>
+    </row>
+    <row r="1460" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1460" s="3" t="s">
+        <v>6009</v>
+      </c>
+      <c r="B1460" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1460" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1460" s="3" t="s">
+        <v>6010</v>
+      </c>
+      <c r="E1460" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1460" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1460" s="3" t="s">
+        <v>6011</v>
+      </c>
+      <c r="H1460" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1460" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1460" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1460" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1460" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1460" s="3" t="s">
+        <v>6008</v>
+      </c>
+      <c r="N1460" s="3"/>
+    </row>
+    <row r="1461" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1461" s="3" t="s">
+        <v>6012</v>
+      </c>
+      <c r="B1461" s="3"/>
+      <c r="C1461" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="D1461" s="3" t="s">
+        <v>6013</v>
+      </c>
+      <c r="E1461" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1461" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="G1461" s="3" t="s">
+        <v>6014</v>
+      </c>
+      <c r="H1461" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1461" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1461" s="3"/>
+      <c r="K1461" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1461" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1461" s="3" t="s">
+        <v>6008</v>
+      </c>
+      <c r="N1461" s="3"/>
+    </row>
+    <row r="1462" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1462" s="3" t="s">
+        <v>6015</v>
+      </c>
+      <c r="B1462" s="3"/>
+      <c r="C1462" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1462" s="3" t="s">
+        <v>6016</v>
+      </c>
+      <c r="E1462" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1462" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G1462" s="3" t="s">
+        <v>6017</v>
+      </c>
+      <c r="H1462" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1462" s="3">
+        <v>49</v>
+      </c>
+      <c r="J1462" s="3"/>
+      <c r="K1462" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1462" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1462" s="3" t="s">
+        <v>6018</v>
+      </c>
+      <c r="N1462" s="3"/>
+    </row>
+    <row r="1463" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1463" s="3" t="s">
+        <v>6019</v>
+      </c>
+      <c r="B1463" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1463" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1463" s="3" t="s">
+        <v>6020</v>
+      </c>
+      <c r="E1463" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1463" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="G1463" s="3" t="s">
+        <v>6021</v>
+      </c>
+      <c r="H1463" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1463" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1463" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1463" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1463" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1463" s="3" t="s">
+        <v>6022</v>
+      </c>
+      <c r="N1463" s="3"/>
+    </row>
+    <row r="1464" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1464" s="3" t="s">
+        <v>6023</v>
+      </c>
+      <c r="B1464" s="3" t="s">
+        <v>3848</v>
+      </c>
+      <c r="C1464" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1464" s="3" t="s">
+        <v>6024</v>
+      </c>
+      <c r="E1464" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1464" s="3" t="s">
+        <v>5139</v>
+      </c>
+      <c r="G1464" s="3" t="s">
+        <v>6025</v>
+      </c>
+      <c r="H1464" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1464" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1464" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1464" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1464" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1464" s="3" t="s">
+        <v>6026</v>
+      </c>
+      <c r="N1464" s="3"/>
+    </row>
+    <row r="1465" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1465" s="3" t="s">
+        <v>6027</v>
+      </c>
+      <c r="B1465" s="3"/>
+      <c r="C1465" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1465" s="3" t="s">
+        <v>6028</v>
+      </c>
+      <c r="E1465" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1465" s="3" t="s">
+        <v>6029</v>
+      </c>
+      <c r="G1465" s="3" t="s">
+        <v>6030</v>
+      </c>
+      <c r="H1465" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1465" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1465" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1465" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1465" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1465" s="3" t="s">
+        <v>6026</v>
+      </c>
+      <c r="N1465" s="3"/>
+    </row>
+    <row r="1466" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1466" s="3" t="s">
+        <v>6031</v>
+      </c>
+      <c r="B1466" s="3" t="s">
+        <v>3848</v>
+      </c>
+      <c r="C1466" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1466" s="3" t="s">
+        <v>6032</v>
+      </c>
+      <c r="E1466" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1466" s="3" t="s">
+        <v>6033</v>
+      </c>
+      <c r="G1466" s="3" t="s">
+        <v>6034</v>
+      </c>
+      <c r="H1466" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1466" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1466" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1466" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1466" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1466" s="3" t="s">
+        <v>6035</v>
+      </c>
+      <c r="N1466" s="3"/>
+    </row>
+    <row r="1467" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1467" s="3" t="s">
+        <v>6036</v>
+      </c>
+      <c r="B1467" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1467" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1467" s="3" t="s">
+        <v>6037</v>
+      </c>
+      <c r="E1467" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1467" s="3" t="s">
+        <v>6038</v>
+      </c>
+      <c r="G1467" s="3" t="s">
+        <v>6039</v>
+      </c>
+      <c r="H1467" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1467" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1467" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1467" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1467" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1467" s="3" t="s">
+        <v>6040</v>
+      </c>
+      <c r="N1467" s="3" t="s">
+        <v>6041</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1468" s="3" t="s">
+        <v>6042</v>
+      </c>
+      <c r="B1468" s="3"/>
+      <c r="C1468" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1468" s="3" t="s">
+        <v>6043</v>
+      </c>
+      <c r="E1468" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1468" s="3" t="s">
+        <v>6044</v>
+      </c>
+      <c r="G1468" s="3" t="s">
+        <v>6045</v>
+      </c>
+      <c r="H1468" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1468" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1468" s="3"/>
+      <c r="K1468" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1468" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1468" s="3" t="s">
+        <v>6022</v>
+      </c>
+      <c r="N1468" s="3"/>
+    </row>
+    <row r="1469" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1469" s="3" t="s">
+        <v>6046</v>
+      </c>
+      <c r="B1469" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1469" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1469" s="3" t="s">
+        <v>6047</v>
+      </c>
+      <c r="E1469" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1469" s="3" t="s">
+        <v>2427</v>
+      </c>
+      <c r="G1469" s="3" t="s">
+        <v>6048</v>
+      </c>
+      <c r="H1469" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1469" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1469" s="3"/>
+      <c r="K1469" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1469" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1469" s="3" t="s">
+        <v>6022</v>
+      </c>
+      <c r="N1469" s="3"/>
+    </row>
+    <row r="1470" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1470" s="3" t="s">
+        <v>6049</v>
+      </c>
+      <c r="B1470" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1470" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1470" s="3" t="s">
+        <v>6050</v>
+      </c>
+      <c r="E1470" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1470" s="3" t="s">
+        <v>6051</v>
+      </c>
+      <c r="G1470" s="3" t="s">
+        <v>6052</v>
+      </c>
+      <c r="H1470" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1470" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1470" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1470" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1470" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1470" s="3" t="s">
+        <v>6022</v>
+      </c>
+      <c r="N1470" s="3"/>
+    </row>
+    <row r="1471" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1471" s="3" t="s">
+        <v>6053</v>
+      </c>
+      <c r="B1471" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1471" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1471" s="3" t="s">
+        <v>6054</v>
+      </c>
+      <c r="E1471" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1471" s="3" t="s">
+        <v>6055</v>
+      </c>
+      <c r="G1471" s="3" t="s">
+        <v>6056</v>
+      </c>
+      <c r="H1471" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1471" s="3">
+        <v>52</v>
+      </c>
+      <c r="J1471" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1471" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1471" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1471" s="3" t="s">
+        <v>6022</v>
+      </c>
+      <c r="N1471" s="3"/>
+    </row>
+    <row r="1472" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1472" s="3" t="s">
+        <v>6057</v>
+      </c>
+      <c r="B1472" s="3"/>
+      <c r="C1472" s="3">
+        <v>150</v>
+      </c>
+      <c r="D1472" s="3" t="s">
+        <v>6058</v>
+      </c>
+      <c r="E1472" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="F1472" s="3" t="s">
+        <v>6059</v>
+      </c>
+      <c r="G1472" s="3" t="s">
+        <v>6060</v>
+      </c>
+      <c r="H1472" s="3"/>
+      <c r="I1472" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1472" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1472" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1472" s="3"/>
+      <c r="M1472" s="3"/>
+      <c r="N1472" s="3"/>
+    </row>
+    <row r="1473" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1473" s="3" t="s">
+        <v>6061</v>
+      </c>
+      <c r="B1473" s="3"/>
+      <c r="C1473" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1473" s="3" t="s">
+        <v>6062</v>
+      </c>
+      <c r="E1473" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1473" s="3" t="s">
+        <v>5201</v>
+      </c>
+      <c r="G1473" s="3" t="s">
+        <v>6063</v>
+      </c>
+      <c r="H1473" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1473" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1473" s="3"/>
+      <c r="K1473" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1473" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1473" s="3" t="s">
+        <v>6064</v>
+      </c>
+      <c r="N1473" s="3"/>
+    </row>
+    <row r="1474" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1474" s="3" t="s">
+        <v>6065</v>
+      </c>
+      <c r="B1474" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C1474" s="3">
+        <v>248</v>
+      </c>
+      <c r="D1474" s="3" t="s">
+        <v>6066</v>
+      </c>
+      <c r="E1474" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1474" s="3" t="s">
+        <v>6067</v>
+      </c>
+      <c r="G1474" s="3" t="s">
+        <v>6068</v>
+      </c>
+      <c r="H1474" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1474" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1474" s="3"/>
+      <c r="K1474" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1474" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1474" s="3" t="s">
+        <v>6069</v>
+      </c>
+      <c r="N1474" s="3"/>
+    </row>
+    <row r="1475" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1475" s="3" t="s">
+        <v>6070</v>
+      </c>
+      <c r="B1475" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1475" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1475" s="3" t="s">
+        <v>6071</v>
+      </c>
+      <c r="E1475" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1475" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="G1475" s="3" t="s">
+        <v>6072</v>
+      </c>
+      <c r="H1475" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1475" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1475" s="3"/>
+      <c r="K1475" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1475" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1475" s="3" t="s">
+        <v>6073</v>
+      </c>
+      <c r="N1475" s="3"/>
+    </row>
+    <row r="1476" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1476" s="3" t="s">
+        <v>6074</v>
+      </c>
+      <c r="B1476" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1476" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1476" s="3" t="s">
+        <v>6075</v>
+      </c>
+      <c r="E1476" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1476" s="3" t="s">
+        <v>6076</v>
+      </c>
+      <c r="G1476" s="3" t="s">
+        <v>6077</v>
+      </c>
+      <c r="H1476" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1476" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1476" s="3"/>
+      <c r="K1476" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1476" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1476" s="3" t="s">
+        <v>6078</v>
+      </c>
+      <c r="N1476" s="3"/>
+    </row>
+    <row r="1477" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1477" s="3" t="s">
+        <v>6079</v>
+      </c>
+      <c r="B1477" s="3" t="s">
+        <v>3848</v>
+      </c>
+      <c r="C1477" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1477" s="3" t="s">
+        <v>6080</v>
+      </c>
+      <c r="E1477" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1477" s="3" t="s">
+        <v>6081</v>
+      </c>
+      <c r="G1477" s="3" t="s">
+        <v>6082</v>
+      </c>
+      <c r="H1477" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1477" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1477" s="3"/>
+      <c r="K1477" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1477" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1477" s="3" t="s">
+        <v>6083</v>
+      </c>
+      <c r="N1477" s="3"/>
+    </row>
+    <row r="1478" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1478" s="3" t="s">
+        <v>6084</v>
+      </c>
+      <c r="B1478" s="3" t="s">
+        <v>3848</v>
+      </c>
+      <c r="C1478" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1478" s="3" t="s">
+        <v>6085</v>
+      </c>
+      <c r="E1478" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1478" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G1478" s="3" t="s">
+        <v>6086</v>
+      </c>
+      <c r="H1478" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1478" s="3">
+        <v>24</v>
+      </c>
+      <c r="J1478" s="3"/>
+      <c r="K1478" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1478" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1478" s="3" t="s">
+        <v>6087</v>
+      </c>
+      <c r="N1478" s="3"/>
+    </row>
+    <row r="1479" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1479" s="3" t="s">
+        <v>6088</v>
+      </c>
+      <c r="B1479" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1479" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1479" s="3" t="s">
+        <v>6089</v>
+      </c>
+      <c r="E1479" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1479" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1479" s="3" t="s">
+        <v>6090</v>
+      </c>
+      <c r="H1479" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1479" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1479" s="3"/>
+      <c r="K1479" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1479" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1479" s="3" t="s">
+        <v>6091</v>
+      </c>
+      <c r="N1479" s="3"/>
+    </row>
+    <row r="1480" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1480" s="3" t="s">
+        <v>6092</v>
+      </c>
+      <c r="B1480" s="3"/>
+      <c r="C1480" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1480" s="3" t="s">
+        <v>6093</v>
+      </c>
+      <c r="E1480" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1480" s="3" t="s">
+        <v>4943</v>
+      </c>
+      <c r="G1480" s="3" t="s">
+        <v>6094</v>
+      </c>
+      <c r="H1480" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1480" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1480" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1480" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1480" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1480" s="3" t="s">
+        <v>6078</v>
+      </c>
+      <c r="N1480" s="3"/>
+    </row>
+    <row r="1481" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1481" s="3" t="s">
+        <v>6095</v>
+      </c>
+      <c r="B1481" s="3"/>
+      <c r="C1481" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1481" s="3" t="s">
+        <v>6096</v>
+      </c>
+      <c r="E1481" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1481" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="G1481" s="3" t="s">
+        <v>6097</v>
+      </c>
+      <c r="H1481" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1481" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1481" s="3"/>
+      <c r="K1481" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1481" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1481" s="3" t="s">
+        <v>6098</v>
+      </c>
+      <c r="N1481" s="3"/>
+    </row>
+    <row r="1482" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1482" s="3" t="s">
+        <v>6099</v>
+      </c>
+      <c r="B1482" s="3"/>
+      <c r="C1482" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1482" s="3" t="s">
+        <v>6100</v>
+      </c>
+      <c r="E1482" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1482" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="G1482" s="3" t="s">
+        <v>6101</v>
+      </c>
+      <c r="H1482" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1482" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1482" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1482" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1482" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1482" s="3" t="s">
+        <v>6102</v>
+      </c>
+      <c r="N1482" s="3"/>
+    </row>
+    <row r="1483" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1483" s="3" t="s">
+        <v>6103</v>
+      </c>
+      <c r="B1483" s="3" t="s">
+        <v>3638</v>
+      </c>
+      <c r="C1483" s="3">
+        <v>206</v>
+      </c>
+      <c r="D1483" s="3" t="s">
+        <v>6104</v>
+      </c>
+      <c r="E1483" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1483" s="3" t="s">
+        <v>6105</v>
+      </c>
+      <c r="G1483" s="3" t="s">
+        <v>6106</v>
+      </c>
+      <c r="H1483" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1483" s="3"/>
+      <c r="J1483" s="3"/>
+      <c r="K1483" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1483" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1483" s="3" t="s">
+        <v>6091</v>
+      </c>
+      <c r="N1483" s="3" t="s">
+        <v>6107</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1484" s="3" t="s">
+        <v>6108</v>
+      </c>
+      <c r="B1484" s="3"/>
+      <c r="C1484" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1484" s="3" t="s">
+        <v>6109</v>
+      </c>
+      <c r="E1484" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1484" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="G1484" s="3" t="s">
+        <v>6110</v>
+      </c>
+      <c r="H1484" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1484" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1484" s="3"/>
+      <c r="K1484" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1484" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1484" s="3" t="s">
+        <v>6111</v>
+      </c>
+      <c r="N1484" s="3"/>
+    </row>
+    <row r="1485" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1485" s="3" t="s">
+        <v>6112</v>
+      </c>
+      <c r="B1485" s="3"/>
+      <c r="C1485" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1485" s="3" t="s">
+        <v>6113</v>
+      </c>
+      <c r="E1485" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1485" s="3" t="s">
+        <v>4713</v>
+      </c>
+      <c r="G1485" s="3" t="s">
+        <v>6114</v>
+      </c>
+      <c r="H1485" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1485" s="3">
+        <v>3</v>
+      </c>
+      <c r="J1485" s="3"/>
+      <c r="K1485" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1485" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1485" s="3" t="s">
+        <v>6115</v>
+      </c>
+      <c r="N1485" s="3"/>
+    </row>
+    <row r="1486" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1486" s="3" t="s">
+        <v>6116</v>
+      </c>
+      <c r="B1486" s="3"/>
+      <c r="C1486" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1486" s="3" t="s">
+        <v>6118</v>
+      </c>
+      <c r="E1486" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1486" s="3" t="s">
+        <v>4578</v>
+      </c>
+      <c r="G1486" s="3" t="s">
+        <v>6119</v>
+      </c>
+      <c r="H1486" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1486" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1486" s="3"/>
+      <c r="K1486" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1486" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1486" s="3" t="s">
+        <v>6120</v>
+      </c>
+      <c r="N1486" s="3"/>
+    </row>
+    <row r="1487" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1487" s="3" t="s">
+        <v>6121</v>
+      </c>
+      <c r="B1487" s="3"/>
+      <c r="C1487" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1487" s="3" t="s">
+        <v>6122</v>
+      </c>
+      <c r="E1487" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1487" s="3" t="s">
+        <v>6123</v>
+      </c>
+      <c r="G1487" s="3" t="s">
+        <v>6124</v>
+      </c>
+      <c r="H1487" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1487" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1487" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1487" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1487" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1487" s="3" t="s">
+        <v>6125</v>
+      </c>
+      <c r="N1487" s="3"/>
+    </row>
+    <row r="1488" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1488" s="3" t="s">
+        <v>6126</v>
+      </c>
+      <c r="B1488" s="3"/>
+      <c r="C1488" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1488" s="3" t="s">
+        <v>6127</v>
+      </c>
+      <c r="E1488" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1488" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G1488" s="3" t="s">
+        <v>6128</v>
+      </c>
+      <c r="H1488" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1488" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1488" s="3"/>
+      <c r="K1488" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1488" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1488" s="3" t="s">
+        <v>6125</v>
+      </c>
+      <c r="N1488" s="3"/>
+    </row>
+    <row r="1489" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1489" s="3" t="s">
+        <v>6129</v>
+      </c>
+      <c r="B1489" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1489" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1489" s="3" t="s">
+        <v>6130</v>
+      </c>
+      <c r="E1489" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="F1489" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1489" s="3" t="s">
+        <v>6131</v>
+      </c>
+      <c r="H1489" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1489" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1489" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1489" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1489" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1489" s="3" t="s">
+        <v>6125</v>
+      </c>
+      <c r="N1489" s="3"/>
+    </row>
+    <row r="1490" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1490" s="3" t="s">
+        <v>6132</v>
+      </c>
+      <c r="B1490" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1490" s="3">
+        <v>214</v>
+      </c>
+      <c r="D1490" s="3" t="s">
+        <v>6133</v>
+      </c>
+      <c r="E1490" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1490" s="3" t="s">
+        <v>6134</v>
+      </c>
+      <c r="G1490" s="3" t="s">
+        <v>6135</v>
+      </c>
+      <c r="H1490" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1490" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1490" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1490" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1490" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1490" s="3" t="s">
+        <v>6136</v>
+      </c>
+      <c r="N1490" s="3"/>
+    </row>
+    <row r="1491" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1491" s="3" t="s">
+        <v>6137</v>
+      </c>
+      <c r="B1491" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C1491" s="3">
+        <v>240</v>
+      </c>
+      <c r="D1491" s="3" t="s">
+        <v>6138</v>
+      </c>
+      <c r="E1491" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1491" s="3" t="s">
+        <v>6139</v>
+      </c>
+      <c r="G1491" s="3" t="s">
+        <v>6140</v>
+      </c>
+      <c r="H1491" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1491" s="3">
+        <v>47</v>
+      </c>
+      <c r="J1491" s="3"/>
+      <c r="K1491" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1491" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1491" s="3" t="s">
+        <v>6141</v>
+      </c>
+      <c r="N1491" s="3"/>
+    </row>
+    <row r="1492" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1492" s="3" t="s">
+        <v>6142</v>
+      </c>
+      <c r="B1492" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1492" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1492" s="3" t="s">
+        <v>6143</v>
+      </c>
+      <c r="E1492" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1492" s="3" t="s">
+        <v>5301</v>
+      </c>
+      <c r="G1492" s="3" t="s">
+        <v>6144</v>
+      </c>
+      <c r="H1492" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1492" s="3">
+        <v>18</v>
+      </c>
+      <c r="J1492" s="3"/>
+      <c r="K1492" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1492" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1492" s="3" t="s">
+        <v>6136</v>
+      </c>
+      <c r="N1492" s="3" t="s">
+        <v>6145</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1493" s="3" t="s">
+        <v>6146</v>
+      </c>
+      <c r="B1493" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1493" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1493" s="3" t="s">
+        <v>6147</v>
+      </c>
+      <c r="E1493" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1493" s="3" t="s">
+        <v>6148</v>
+      </c>
+      <c r="G1493" s="3" t="s">
+        <v>6149</v>
+      </c>
+      <c r="H1493" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1493" s="3">
+        <v>54</v>
+      </c>
+      <c r="J1493" s="3"/>
+      <c r="K1493" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1493" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1493" s="3" t="s">
+        <v>6141</v>
+      </c>
+      <c r="N1493" s="3"/>
+    </row>
+    <row r="1494" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1494" s="3" t="s">
+        <v>6150</v>
+      </c>
+      <c r="B1494" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1494" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1494" s="3" t="s">
+        <v>6151</v>
+      </c>
+      <c r="E1494" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1494" s="3" t="s">
+        <v>6152</v>
+      </c>
+      <c r="G1494" s="3" t="s">
+        <v>6153</v>
+      </c>
+      <c r="H1494" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1494" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1494" s="3"/>
+      <c r="K1494" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1494" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1494" s="3" t="s">
+        <v>6141</v>
+      </c>
+      <c r="N1494" s="3"/>
+    </row>
+    <row r="1495" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1495" s="3" t="s">
+        <v>6154</v>
+      </c>
+      <c r="B1495" s="3"/>
+      <c r="C1495" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1495" s="3" t="s">
+        <v>6155</v>
+      </c>
+      <c r="E1495" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1495" s="3" t="s">
+        <v>4457</v>
+      </c>
+      <c r="G1495" s="3" t="s">
+        <v>6156</v>
+      </c>
+      <c r="H1495" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1495" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1495" s="3"/>
+      <c r="K1495" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1495" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1495" s="3" t="s">
+        <v>6141</v>
+      </c>
+      <c r="N1495" s="3"/>
+    </row>
+    <row r="1496" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1496" s="3" t="s">
+        <v>6157</v>
+      </c>
+      <c r="B1496" s="3"/>
+      <c r="C1496" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1496" s="3" t="s">
+        <v>6158</v>
+      </c>
+      <c r="E1496" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1496" s="3" t="s">
+        <v>6159</v>
+      </c>
+      <c r="G1496" s="3" t="s">
+        <v>6160</v>
+      </c>
+      <c r="H1496" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1496" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1496" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1496" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1496" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1496" s="3" t="s">
+        <v>6161</v>
+      </c>
+      <c r="N1496" s="3"/>
+    </row>
+    <row r="1497" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1497" s="3" t="s">
+        <v>6162</v>
+      </c>
+      <c r="B1497" s="3"/>
+      <c r="C1497" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1497" s="3" t="s">
+        <v>6163</v>
+      </c>
+      <c r="E1497" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1497" s="3" t="s">
+        <v>5647</v>
+      </c>
+      <c r="G1497" s="3" t="s">
+        <v>6164</v>
+      </c>
+      <c r="H1497" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1497" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1497" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1497" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1497" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1497" s="3" t="s">
+        <v>6161</v>
+      </c>
+      <c r="N1497" s="3"/>
+    </row>
+    <row r="1498" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1498" s="3" t="s">
+        <v>6165</v>
+      </c>
+      <c r="B1498" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C1498" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1498" s="3" t="s">
+        <v>6166</v>
+      </c>
+      <c r="E1498" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1498" s="3" t="s">
+        <v>6167</v>
+      </c>
+      <c r="G1498" s="3" t="s">
+        <v>6168</v>
+      </c>
+      <c r="H1498" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1498" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1498" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1498" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1498" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1498" s="3" t="s">
+        <v>6169</v>
+      </c>
+      <c r="N1498" s="3"/>
+    </row>
+    <row r="1499" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1499" s="3" t="s">
+        <v>6170</v>
+      </c>
+      <c r="B1499" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1499" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1499" s="3" t="s">
+        <v>6171</v>
+      </c>
+      <c r="E1499" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1499" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="G1499" s="3" t="s">
+        <v>6172</v>
+      </c>
+      <c r="H1499" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1499" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1499" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1499" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1499" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1499" s="3" t="s">
+        <v>6173</v>
+      </c>
+      <c r="N1499" s="3"/>
+    </row>
+    <row r="1500" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1500" s="3" t="s">
+        <v>6170</v>
+      </c>
+      <c r="B1500" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1500" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1500" s="3" t="s">
+        <v>6174</v>
+      </c>
+      <c r="E1500" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1500" s="3" t="s">
+        <v>6175</v>
+      </c>
+      <c r="G1500" s="3" t="s">
+        <v>6176</v>
+      </c>
+      <c r="H1500" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1500" s="3">
+        <v>39</v>
+      </c>
+      <c r="J1500" s="3"/>
+      <c r="K1500" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1500" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1500" s="3" t="s">
+        <v>6173</v>
+      </c>
+      <c r="N1500" s="3"/>
+    </row>
+    <row r="1501" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1501" s="3" t="s">
+        <v>6177</v>
+      </c>
+      <c r="B1501" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C1501" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1501" s="3" t="s">
+        <v>6178</v>
+      </c>
+      <c r="E1501" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1501" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="G1501" s="3" t="s">
+        <v>6179</v>
+      </c>
+      <c r="H1501" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1501" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1501" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1501" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1501" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1501" s="3" t="s">
+        <v>6180</v>
+      </c>
+      <c r="N1501" s="3"/>
+    </row>
+    <row r="1502" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1502" s="3" t="s">
+        <v>6181</v>
+      </c>
+      <c r="B1502" s="3"/>
+      <c r="C1502" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1502" s="3" t="s">
+        <v>6182</v>
+      </c>
+      <c r="E1502" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1502" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="G1502" s="3" t="s">
+        <v>6183</v>
+      </c>
+      <c r="H1502" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1502" s="3"/>
+      <c r="J1502" s="3"/>
+      <c r="K1502" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1502" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1502" s="3" t="s">
+        <v>6184</v>
+      </c>
+      <c r="N1502" s="3"/>
+    </row>
+    <row r="1503" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1503" s="3" t="s">
+        <v>6185</v>
+      </c>
+      <c r="B1503" s="3"/>
+      <c r="C1503" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1503" s="3" t="s">
+        <v>6186</v>
+      </c>
+      <c r="E1503" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1503" s="3" t="s">
+        <v>6187</v>
+      </c>
+      <c r="G1503" s="3" t="s">
+        <v>6188</v>
+      </c>
+      <c r="H1503" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1503" s="3"/>
+      <c r="J1503" s="3"/>
+      <c r="K1503" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1503" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1503" s="3" t="s">
+        <v>6184</v>
+      </c>
+      <c r="N1503" s="3"/>
+    </row>
+    <row r="1504" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1504" s="3" t="s">
+        <v>6189</v>
+      </c>
+      <c r="B1504" s="3"/>
+      <c r="C1504" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1504" s="3" t="s">
+        <v>6190</v>
+      </c>
+      <c r="E1504" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1504" s="3" t="s">
+        <v>6191</v>
+      </c>
+      <c r="G1504" s="3" t="s">
+        <v>6192</v>
+      </c>
+      <c r="H1504" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1504" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1504" s="3"/>
+      <c r="K1504" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1504" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1504" s="3" t="s">
+        <v>6184</v>
+      </c>
+      <c r="N1504" s="3"/>
+    </row>
+    <row r="1505" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1505" s="3" t="s">
+        <v>6193</v>
+      </c>
+      <c r="B1505" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C1505" s="3">
+        <v>248</v>
+      </c>
+      <c r="D1505" s="3" t="s">
+        <v>6194</v>
+      </c>
+      <c r="E1505" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1505" s="3" t="s">
+        <v>6195</v>
+      </c>
+      <c r="G1505" s="3" t="s">
+        <v>6196</v>
+      </c>
+      <c r="H1505" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1505" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1505" s="3"/>
+      <c r="K1505" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1505" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1505" s="3" t="s">
+        <v>6184</v>
+      </c>
+      <c r="N1505" s="3"/>
+    </row>
+    <row r="1506" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1506" s="3" t="s">
+        <v>6197</v>
+      </c>
+      <c r="B1506" s="3"/>
+      <c r="C1506" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1506" s="3" t="s">
+        <v>6198</v>
+      </c>
+      <c r="E1506" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1506" s="3" t="s">
+        <v>5013</v>
+      </c>
+      <c r="G1506" s="3" t="s">
+        <v>6199</v>
+      </c>
+      <c r="H1506" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1506" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1506" s="3"/>
+      <c r="K1506" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1506" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1506" s="3" t="s">
+        <v>6200</v>
+      </c>
+      <c r="N1506" s="3"/>
+    </row>
+    <row r="1507" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1507" s="3" t="s">
+        <v>6201</v>
+      </c>
+      <c r="B1507" s="3"/>
+      <c r="C1507" s="3">
+        <v>234</v>
+      </c>
+      <c r="D1507" s="3" t="s">
+        <v>6202</v>
+      </c>
+      <c r="E1507" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1507" s="3" t="s">
+        <v>6203</v>
+      </c>
+      <c r="G1507" s="3" t="s">
+        <v>6204</v>
+      </c>
+      <c r="H1507" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1507" s="3">
+        <v>26</v>
+      </c>
+      <c r="J1507" s="3"/>
+      <c r="K1507" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1507" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1507" s="3" t="s">
+        <v>6200</v>
+      </c>
+      <c r="N1507" s="3"/>
+    </row>
+    <row r="1508" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1508" s="3" t="s">
+        <v>6205</v>
+      </c>
+      <c r="B1508" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1508" s="3">
+        <v>250</v>
+      </c>
+      <c r="D1508" s="3" t="s">
+        <v>6206</v>
+      </c>
+      <c r="E1508" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1508" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1508" s="3" t="s">
+        <v>6207</v>
+      </c>
+      <c r="H1508" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1508" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1508" s="3"/>
+      <c r="K1508" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1508" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1508" s="3" t="s">
+        <v>6200</v>
+      </c>
+      <c r="N1508" s="3"/>
+    </row>
+    <row r="1509" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1509" s="3" t="s">
+        <v>6208</v>
+      </c>
+      <c r="B1509" s="3"/>
+      <c r="C1509" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1509" s="3" t="s">
+        <v>6209</v>
+      </c>
+      <c r="E1509" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1509" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G1509" s="3" t="s">
+        <v>6210</v>
+      </c>
+      <c r="H1509" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1509" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1509" s="3"/>
+      <c r="K1509" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1509" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1509" s="3" t="s">
+        <v>6211</v>
+      </c>
+      <c r="N1509" s="3"/>
+    </row>
+    <row r="1510" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1510" s="3" t="s">
+        <v>6212</v>
+      </c>
+      <c r="B1510" s="3"/>
+      <c r="C1510" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1510" s="3" t="s">
+        <v>6213</v>
+      </c>
+      <c r="E1510" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1510" s="3" t="s">
+        <v>6214</v>
+      </c>
+      <c r="G1510" s="3" t="s">
+        <v>6215</v>
+      </c>
+      <c r="H1510" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1510" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1510" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1510" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1510" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1510" s="3" t="s">
+        <v>6211</v>
+      </c>
+      <c r="N1510" s="3"/>
+    </row>
+    <row r="1511" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1511" s="3" t="s">
+        <v>6216</v>
+      </c>
+      <c r="B1511" s="3" t="s">
+        <v>3638</v>
+      </c>
+      <c r="C1511" s="3">
+        <v>234</v>
+      </c>
+      <c r="D1511" s="3" t="s">
+        <v>6217</v>
+      </c>
+      <c r="E1511" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1511" s="3" t="s">
+        <v>6218</v>
+      </c>
+      <c r="G1511" s="3" t="s">
+        <v>6219</v>
+      </c>
+      <c r="H1511" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1511" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1511" s="3"/>
+      <c r="K1511" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1511" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1511" s="3" t="s">
+        <v>6220</v>
+      </c>
+      <c r="N1511" s="3" t="s">
+        <v>6221</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1512" s="3" t="s">
+        <v>6222</v>
+      </c>
+      <c r="B1512" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C1512" s="3">
+        <v>218</v>
+      </c>
+      <c r="D1512" s="3" t="s">
+        <v>6223</v>
+      </c>
+      <c r="E1512" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1512" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="G1512" s="3" t="s">
+        <v>6224</v>
+      </c>
+      <c r="H1512" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1512" s="3">
+        <v>47</v>
+      </c>
+      <c r="J1512" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1512" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1512" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1512" s="3" t="s">
+        <v>6225</v>
+      </c>
+      <c r="N1512" s="3" t="s">
+        <v>6226</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1513" s="3" t="s">
+        <v>6227</v>
+      </c>
+      <c r="B1513" s="3"/>
+      <c r="C1513" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1513" s="3" t="s">
+        <v>6228</v>
+      </c>
+      <c r="E1513" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1513" s="3" t="s">
+        <v>4563</v>
+      </c>
+      <c r="G1513" s="3" t="s">
+        <v>6229</v>
+      </c>
+      <c r="H1513" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1513" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1513" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1513" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1513" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1513" s="3" t="s">
+        <v>6230</v>
+      </c>
+      <c r="N1513" s="3"/>
+    </row>
+    <row r="1514" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1514" s="3" t="s">
+        <v>6227</v>
+      </c>
+      <c r="B1514" s="3"/>
+      <c r="C1514" s="3">
+        <v>212</v>
+      </c>
+      <c r="D1514" s="3" t="s">
+        <v>6231</v>
+      </c>
+      <c r="E1514" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1514" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="G1514" s="3" t="s">
+        <v>6232</v>
+      </c>
+      <c r="H1514" s="3"/>
+      <c r="I1514" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1514" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1514" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1514" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1514" s="3" t="s">
+        <v>6230</v>
+      </c>
+      <c r="N1514" s="3"/>
+    </row>
+    <row r="1515" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1515" s="3" t="s">
+        <v>6233</v>
+      </c>
+      <c r="B1515" s="3"/>
+      <c r="C1515" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1515" s="3" t="s">
+        <v>6234</v>
+      </c>
+      <c r="E1515" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1515" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G1515" s="3" t="s">
+        <v>6235</v>
+      </c>
+      <c r="H1515" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1515" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1515" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1515" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1515" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1515" s="3" t="s">
+        <v>6230</v>
+      </c>
+      <c r="N1515" s="3"/>
+    </row>
+    <row r="1516" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1516" s="3" t="s">
+        <v>6236</v>
+      </c>
+      <c r="B1516" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1516" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1516" s="3" t="s">
+        <v>6237</v>
+      </c>
+      <c r="E1516" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1516" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1516" s="3" t="s">
+        <v>6238</v>
+      </c>
+      <c r="H1516" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1516" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1516" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1516" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1516" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1516" s="3" t="s">
+        <v>6230</v>
+      </c>
+      <c r="N1516" s="3"/>
+    </row>
+    <row r="1517" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1517" s="3" t="s">
+        <v>6239</v>
+      </c>
+      <c r="B1517" s="3"/>
+      <c r="C1517" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1517" s="3" t="s">
+        <v>6240</v>
+      </c>
+      <c r="E1517" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1517" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G1517" s="3" t="s">
+        <v>6241</v>
+      </c>
+      <c r="H1517" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1517" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1517" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1517" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1517" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1517" s="3" t="s">
+        <v>6230</v>
+      </c>
+      <c r="N1517" s="3"/>
+    </row>
+    <row r="1518" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1518" s="3" t="s">
+        <v>6242</v>
+      </c>
+      <c r="B1518" s="3"/>
+      <c r="C1518" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1518" s="3" t="s">
+        <v>6243</v>
+      </c>
+      <c r="E1518" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1518" s="3" t="s">
+        <v>6244</v>
+      </c>
+      <c r="G1518" s="3" t="s">
+        <v>6245</v>
+      </c>
+      <c r="H1518" s="3"/>
+      <c r="I1518" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1518" s="3"/>
+      <c r="K1518" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1518" s="3"/>
+      <c r="M1518" s="3"/>
+      <c r="N1518" s="3"/>
+    </row>
+    <row r="1519" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1519" s="3" t="s">
+        <v>6246</v>
+      </c>
+      <c r="B1519" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1519" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1519" s="3" t="s">
+        <v>6247</v>
+      </c>
+      <c r="E1519" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1519" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="G1519" s="3" t="s">
+        <v>6248</v>
+      </c>
+      <c r="H1519" s="3"/>
+      <c r="I1519" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1519" s="3"/>
+      <c r="K1519" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1519" s="3"/>
+      <c r="M1519" s="3"/>
+      <c r="N1519" s="3"/>
+    </row>
+    <row r="1520" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1520" s="3" t="s">
+        <v>6249</v>
+      </c>
+      <c r="B1520" s="3"/>
+      <c r="C1520" s="3">
+        <v>168</v>
+      </c>
+      <c r="D1520" s="3" t="s">
+        <v>6250</v>
+      </c>
+      <c r="E1520" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1520" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G1520" s="3" t="s">
+        <v>6251</v>
+      </c>
+      <c r="H1520" s="3"/>
+      <c r="I1520" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1520" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1520" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1520" s="3"/>
+      <c r="M1520" s="3"/>
+      <c r="N1520" s="3"/>
+    </row>
+    <row r="1521" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1521" s="3" t="s">
+        <v>6252</v>
+      </c>
+      <c r="B1521" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1521" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1521" s="3" t="s">
+        <v>6253</v>
+      </c>
+      <c r="E1521" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1521" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="G1521" s="3" t="s">
+        <v>6254</v>
+      </c>
+      <c r="H1521" s="3"/>
+      <c r="I1521" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1521" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1521" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1521" s="3"/>
+      <c r="M1521" s="3"/>
+      <c r="N1521" s="3"/>
+    </row>
+    <row r="1522" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1522" s="3" t="s">
+        <v>6255</v>
+      </c>
+      <c r="B1522" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C1522" s="3">
+        <v>310</v>
+      </c>
+      <c r="D1522" s="3" t="s">
+        <v>6256</v>
+      </c>
+      <c r="E1522" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1522" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G1522" s="3" t="s">
+        <v>6257</v>
+      </c>
+      <c r="H1522" s="3"/>
+      <c r="I1522" s="3"/>
+      <c r="J1522" s="3"/>
+      <c r="K1522" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1522" s="3"/>
+      <c r="M1522" s="3"/>
+      <c r="N1522" s="3"/>
+    </row>
+    <row r="1523" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1523" s="3" t="s">
+        <v>6258</v>
+      </c>
+      <c r="B1523" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C1523" s="3">
+        <v>248</v>
+      </c>
+      <c r="D1523" s="3" t="s">
+        <v>6259</v>
+      </c>
+      <c r="E1523" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1523" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G1523" s="3" t="s">
+        <v>6260</v>
+      </c>
+      <c r="H1523" s="3"/>
+      <c r="I1523" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1523" s="3"/>
+      <c r="K1523" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1523" s="3"/>
+      <c r="M1523" s="3"/>
+      <c r="N1523" s="3"/>
+    </row>
+    <row r="1524" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1524" s="3" t="s">
+        <v>6261</v>
+      </c>
+      <c r="B1524" s="3"/>
+      <c r="C1524" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1524" s="3" t="s">
+        <v>6262</v>
+      </c>
+      <c r="E1524" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1524" s="3" t="s">
+        <v>6263</v>
+      </c>
+      <c r="G1524" s="3" t="s">
+        <v>6264</v>
+      </c>
+      <c r="H1524" s="3"/>
+      <c r="I1524" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1524" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1524" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1524" s="3"/>
+      <c r="M1524" s="3"/>
+      <c r="N1524" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
